--- a/evaluations/classification/classification_results_LATE_FUSION_tier3_GV_CAL.xlsx
+++ b/evaluations/classification/classification_results_LATE_FUSION_tier3_GV_CAL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T94"/>
+  <dimension ref="A1:T124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,22 +533,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C2" t="n">
-        <v>182</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -559,46 +555,42 @@
         </is>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>200</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>24.42</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9442</v>
+        <v>0.4894</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9712</v>
+        <v>0.8085</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9445</v>
+        <v>0.4043</v>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -609,33 +601,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>200</v>
@@ -648,33 +636,29 @@
       <c r="K3" t="n">
         <v>200</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>144.85</v>
+        <v>0.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9823</v>
+        <v>0.1489</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9907</v>
+        <v>0.3617</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9815</v>
+        <v>0.1149</v>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -685,27 +669,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C4" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
@@ -720,33 +708,29 @@
       <c r="K4" t="n">
         <v>200</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1.39</v>
+        <v>0.37</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9712</v>
+        <v>0.4468</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9898</v>
+        <v>0.7872</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9694</v>
+        <v>0.3688</v>
       </c>
       <c r="Q4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -757,14 +741,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C5" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -775,13 +759,9 @@
         <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>0</v>
       </c>
@@ -796,33 +776,29 @@
       <c r="K5" t="n">
         <v>200</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>6.09</v>
+        <v>0.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9749</v>
+        <v>0.2128</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9898</v>
+        <v>0.4468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9744</v>
+        <v>0.1738</v>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -833,22 +809,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>182</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -862,43 +834,39 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>200</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>38.53</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9395</v>
+        <v>0.4894</v>
       </c>
       <c r="O6" t="n">
-        <v>0.974</v>
+        <v>0.8085</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9394</v>
+        <v>0.4043</v>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -909,14 +877,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -927,11 +895,15 @@
         <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>200</v>
@@ -944,33 +916,29 @@
       <c r="K7" t="n">
         <v>200</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>8.42</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9721</v>
+        <v>0.5957</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9916</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9702</v>
+        <v>0.5203</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -981,14 +949,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -999,54 +967,46 @@
         <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>200</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>14.05</v>
+        <v>3.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0.946</v>
+        <v>0.5532</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9702</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9466</v>
+        <v>0.4787</v>
       </c>
       <c r="Q8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1057,33 +1017,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>200</v>
@@ -1096,33 +1052,29 @@
       <c r="K9" t="n">
         <v>200</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>184.86</v>
+        <v>0.14</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9795</v>
+        <v>0.1489</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9907</v>
+        <v>0.2979</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9782</v>
+        <v>0.1206</v>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1133,18 +1085,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>atrw</t>
+          <t>amvrakikosturtles</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4340</v>
+        <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>47</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1155,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>200</v>
@@ -1168,33 +1120,29 @@
       <c r="K10" t="n">
         <v>200</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>82.81</v>
+        <v>0.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9805</v>
+        <v>0.1489</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9907</v>
+        <v>0.4255</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9794</v>
+        <v>0.1135</v>
       </c>
       <c r="Q10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1216,21 +1164,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>aliked+superpoint</t>
         </is>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1240,22 +1192,18 @@
       <c r="K11" t="n">
         <v>200</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>2.39</v>
+        <v>14.84</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9656</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9879</v>
+        <v>0.9916</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9625</v>
+        <v>0.98</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -1288,18 +1236,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>200</v>
@@ -1318,16 +1270,16 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>144.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9684</v>
+        <v>0.9823</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9805</v>
+        <v>0.9907</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9815</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
@@ -1349,14 +1301,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>belugaid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4625</v>
+        <v>4340</v>
       </c>
       <c r="C13" t="n">
-        <v>788</v>
+        <v>182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1375,35 +1327,31 @@
         </is>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>200</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>10.22</v>
+        <v>67.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6656</v>
+        <v>0.9805</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.9916</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6276</v>
+        <v>0.9787</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1425,22 +1373,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -1451,46 +1395,42 @@
         </is>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>200</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>0.17</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9353</v>
+        <v>0.9581</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9765</v>
+        <v>0.973</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9272</v>
+        <v>0.9567</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1501,40 +1441,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E15" t="b">
         <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1546,27 +1482,27 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3.74</v>
+        <v>2.39</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9235</v>
+        <v>0.9656</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9879</v>
       </c>
       <c r="P15" t="n">
-        <v>0.923</v>
+        <v>0.9625</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1577,36 +1513,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E16" t="b">
         <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1614,7 +1546,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1622,27 +1554,27 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>21.34</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8882</v>
+        <v>0.9684</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1653,14 +1585,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1682,43 +1614,39 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>200</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>6.02</v>
+        <v>101.32</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9294</v>
+        <v>0.9823</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9765</v>
+        <v>0.9907</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9221</v>
+        <v>0.9815</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1729,14 +1657,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1747,18 +1675,22 @@
         <v>1</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1770,27 +1702,27 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>10.14</v>
+        <v>24.42</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8882</v>
+        <v>0.9442</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9529</v>
+        <v>0.9712</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8841</v>
+        <v>0.9445</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1801,14 +1733,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1827,14 +1759,14 @@
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1846,27 +1778,27 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4.22</v>
+        <v>6.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9412</v>
+        <v>0.9749</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9765</v>
+        <v>0.9898</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9744</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1877,32 +1809,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1918,27 +1850,27 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.02</v>
+        <v>82.81</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8471</v>
+        <v>0.9805</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9529</v>
+        <v>0.9907</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8423</v>
+        <v>0.9794</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1949,40 +1881,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E21" t="b">
         <v>1</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1994,27 +1922,27 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4.26</v>
+        <v>1.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9176</v>
+        <v>0.9712</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9765</v>
+        <v>0.9898</v>
       </c>
       <c r="P21" t="n">
-        <v>0.912</v>
+        <v>0.9694</v>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2025,14 +1953,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2058,7 +1986,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2070,27 +1998,27 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>38.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9</v>
+        <v>0.9395</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9765</v>
+        <v>0.974</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8932</v>
+        <v>0.9394</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2101,14 +2029,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2119,22 +2047,18 @@
         <v>1</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2146,27 +2070,27 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9294</v>
+        <v>0.9721</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9765</v>
+        <v>0.9916</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9248</v>
+        <v>0.9702</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2177,36 +2101,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E24" t="b">
         <v>1</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2218,27 +2146,27 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.36</v>
+        <v>14.05</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7353</v>
+        <v>0.946</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9176</v>
+        <v>0.9702</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7184</v>
+        <v>0.9466</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2249,18 +2177,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked+superpoint</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -2282,39 +2210,35 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K25" t="n">
         <v>200</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>4.15</v>
+        <v>12.38</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9059</v>
+        <v>0.9823</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9588</v>
+        <v>0.9944</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8991</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2325,29 +2249,33 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>atrw</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>916</v>
+        <v>4340</v>
       </c>
       <c r="C26" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>200</v>
@@ -2366,27 +2294,27 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.46</v>
+        <v>184.86</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7706</v>
+        <v>0.9795</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9176</v>
+        <v>0.9907</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7611</v>
+        <v>0.9782</v>
       </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2397,14 +2325,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>chicks4freeid</t>
+          <t>belugaid</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>916</v>
+        <v>4625</v>
       </c>
       <c r="C27" t="n">
-        <v>48</v>
+        <v>788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2423,7 +2351,7 @@
         </is>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>50</v>
@@ -2442,27 +2370,27 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>29.91</v>
+        <v>10.22</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9353</v>
+        <v>0.6656</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.6276</v>
       </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2506,7 +2434,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2514,7 +2442,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.72</v>
+        <v>0.02</v>
       </c>
       <c r="N28" t="n">
         <v>0.8471</v>
@@ -2563,18 +2491,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2586,16 +2518,16 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1.22</v>
+        <v>29.91</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7824</v>
+        <v>0.9353</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7712</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -2662,7 +2594,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
         <v>0.9</v>
@@ -2722,11 +2654,11 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2738,16 +2670,16 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>40.52</v>
+        <v>6.05</v>
       </c>
       <c r="N31" t="n">
-        <v>0.9176</v>
+        <v>0.9294</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9529</v>
+        <v>0.9765</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9176</v>
+        <v>0.9248</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
@@ -2778,13 +2710,9 @@
       <c r="C32" t="n">
         <v>48</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -2808,22 +2736,18 @@
       <c r="K32" t="n">
         <v>200</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>1.22</v>
+        <v>0.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8471</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9529</v>
       </c>
       <c r="P32" t="n">
-        <v>0.838</v>
+        <v>0.8434</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
@@ -2856,18 +2780,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>200</v>
@@ -2886,16 +2814,16 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.51</v>
+        <v>40.52</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6706</v>
+        <v>0.9176</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9059</v>
+        <v>0.9529</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6646</v>
+        <v>0.9176</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -2935,22 +2863,18 @@
         <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2962,16 +2886,16 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3.78</v>
+        <v>10.14</v>
       </c>
       <c r="N34" t="n">
-        <v>0.9</v>
+        <v>0.8882</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9765</v>
+        <v>0.9529</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8932</v>
+        <v>0.8841</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -2993,40 +2917,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3038,23 +2958,23 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>9.800000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="N35" t="n">
-        <v>0.981</v>
+        <v>0.6706</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9973</v>
+        <v>0.9059</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9838</v>
+        <v>0.6646</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S35" t="b">
@@ -3069,32 +2989,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3102,7 +3022,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3110,23 +3030,23 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2.98</v>
+        <v>0.72</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8753</v>
+        <v>0.8471</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9675</v>
+        <v>0.9529</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8824</v>
+        <v>0.8423</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S36" t="b">
@@ -3141,36 +3061,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>1</v>
       </c>
       <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -3182,23 +3106,23 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1.73</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7696</v>
+        <v>0.9235</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9051</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8026</v>
+        <v>0.923</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S37" t="b">
@@ -3213,14 +3137,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,14 +3163,14 @@
         </is>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3258,23 +3182,23 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>9.69</v>
+        <v>1.22</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9973</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9805</v>
+        <v>0.838</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S38" t="b">
@@ -3289,31 +3213,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>1</v>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="b">
         <v>0</v>
       </c>
@@ -3334,23 +3254,23 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>0.36</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8753</v>
+        <v>0.7353</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9675</v>
+        <v>0.9176</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8834</v>
+        <v>0.7184</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S39" t="b">
@@ -3365,18 +3285,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -3406,23 +3326,23 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.61</v>
+        <v>1.22</v>
       </c>
       <c r="N40" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.7824</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9756</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9372</v>
+        <v>0.7712</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S40" t="b">
@@ -3437,40 +3357,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>1</v>
       </c>
       <c r="F41" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3482,23 +3398,23 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>14.52</v>
+        <v>0.46</v>
       </c>
       <c r="N41" t="n">
-        <v>0.9756</v>
+        <v>0.7706</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9973</v>
+        <v>0.9176</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9788</v>
+        <v>0.7611</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S41" t="b">
@@ -3513,14 +3429,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3542,11 +3458,11 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3558,23 +3474,23 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>61.43</v>
+        <v>4.22</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9412</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0.9765</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9876</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S42" t="b">
@@ -3589,14 +3505,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3634,23 +3550,23 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>113.01</v>
+        <v>6.02</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9294</v>
       </c>
       <c r="O43" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9765</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9789</v>
+        <v>0.9221</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S43" t="b">
@@ -3665,14 +3581,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3683,18 +3599,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3706,23 +3626,23 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>37.46</v>
+        <v>3.78</v>
       </c>
       <c r="N44" t="n">
-        <v>0.981</v>
+        <v>0.9</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0.9765</v>
       </c>
       <c r="P44" t="n">
-        <v>0.9821</v>
+        <v>0.8932</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S44" t="b">
@@ -3737,29 +3657,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cowdataset</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1019</v>
+        <v>916</v>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>1</v>
       </c>
       <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>200</v>
@@ -3772,29 +3696,25 @@
       <c r="K45" t="n">
         <v>200</v>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>0.77</v>
+        <v>12.66</v>
       </c>
       <c r="N45" t="n">
-        <v>0.9079</v>
+        <v>0.9176</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9675</v>
+        <v>0.9529</v>
       </c>
       <c r="P45" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9176</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S45" t="b">
@@ -3809,18 +3729,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ctai</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4145</v>
+        <v>916</v>
       </c>
       <c r="C46" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked+superpoint</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -3835,46 +3755,42 @@
         </is>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K46" t="n">
         <v>200</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>7.51</v>
+        <v>10.58</v>
       </c>
       <c r="N46" t="n">
-        <v>0.8875</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9282</v>
+        <v>0.9529</v>
       </c>
       <c r="P46" t="n">
-        <v>0.8982</v>
+        <v>0.9119</v>
       </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3885,14 +3801,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ctai</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4145</v>
+        <v>916</v>
       </c>
       <c r="C47" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3918,11 +3834,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3930,27 +3846,27 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>24.55</v>
+        <v>21.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0.8821</v>
+        <v>0.8882</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9271</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="P47" t="n">
-        <v>0.8888</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="Q47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3961,14 +3877,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1686</v>
+        <v>916</v>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3979,18 +3895,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -4002,27 +3922,27 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>29.2</v>
+        <v>4.15</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8818</v>
+        <v>0.9059</v>
       </c>
       <c r="O48" t="n">
-        <v>0.9598</v>
+        <v>0.9588</v>
       </c>
       <c r="P48" t="n">
-        <v>0.88</v>
+        <v>0.8991</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4033,36 +3953,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1686</v>
+        <v>916</v>
       </c>
       <c r="C49" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E49" t="b">
         <v>1</v>
       </c>
       <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -4074,27 +3998,27 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6832</v>
+        <v>0.9353</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8723</v>
+        <v>0.9765</v>
       </c>
       <c r="P49" t="n">
-        <v>0.6791</v>
+        <v>0.9272</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4105,36 +4029,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1686</v>
+        <v>916</v>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E50" t="b">
         <v>1</v>
       </c>
       <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -4146,27 +4074,27 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1.23</v>
+        <v>4.26</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6478</v>
+        <v>0.9176</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8227</v>
+        <v>0.9765</v>
       </c>
       <c r="P50" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="Q50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4177,29 +4105,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1686</v>
+        <v>916</v>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>aliked+superpoint</t>
         </is>
       </c>
       <c r="E51" t="b">
         <v>1</v>
       </c>
       <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>200</v>
@@ -4212,33 +4144,29 @@
       <c r="K51" t="n">
         <v>200</v>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>0.41</v>
+        <v>9.18</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6974</v>
+        <v>0.8882</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8345</v>
+        <v>0.9765</v>
       </c>
       <c r="P51" t="n">
-        <v>0.6947</v>
+        <v>0.8822</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4249,14 +4177,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>chicks4freeid</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1686</v>
+        <v>916</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4275,10 +4203,10 @@
         </is>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4294,27 +4222,27 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.69</v>
       </c>
       <c r="N52" t="n">
-        <v>0.9905</v>
+        <v>0.9</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9905</v>
+        <v>0.9765</v>
       </c>
       <c r="P52" t="n">
-        <v>0.9905</v>
+        <v>0.8932</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>similarity-aware</t>
         </is>
       </c>
       <c r="S52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4325,14 +4253,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1686</v>
+        <v>1019</v>
       </c>
       <c r="C53" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4343,11 +4271,15 @@
         <v>1</v>
       </c>
       <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>200</v>
@@ -4366,27 +4298,27 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>35.31</v>
+        <v>61.43</v>
       </c>
       <c r="N53" t="n">
-        <v>0.7612</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9054</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.7568</v>
+        <v>0.9876</v>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4397,18 +4329,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1686</v>
+        <v>1019</v>
       </c>
       <c r="C54" t="n">
-        <v>24</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -4419,14 +4355,14 @@
         </is>
       </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -4438,27 +4374,27 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.07000000000000001</v>
+        <v>14.52</v>
       </c>
       <c r="N54" t="n">
-        <v>0.9882</v>
+        <v>0.9756</v>
       </c>
       <c r="O54" t="n">
-        <v>0.9882</v>
+        <v>0.9973</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9882</v>
+        <v>0.9788</v>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4469,33 +4405,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1686</v>
+        <v>1019</v>
       </c>
       <c r="C55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="b">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>200</v>
@@ -4514,27 +4446,27 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>29.34</v>
+        <v>0.61</v>
       </c>
       <c r="N55" t="n">
-        <v>0.9858</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9929</v>
+        <v>0.9756</v>
       </c>
       <c r="P55" t="n">
-        <v>0.9858</v>
+        <v>0.9372</v>
       </c>
       <c r="Q55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4545,14 +4477,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>czoo</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1686</v>
+        <v>1019</v>
       </c>
       <c r="C56" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4563,18 +4495,22 @@
         <v>1</v>
       </c>
       <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4586,27 +4522,27 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>2.66</v>
+        <v>9.69</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7612</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9054</v>
+        <v>0.9973</v>
       </c>
       <c r="P56" t="n">
-        <v>0.7568</v>
+        <v>0.9805</v>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4617,36 +4553,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C57" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E57" t="b">
         <v>1</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -4658,23 +4598,23 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>2.47</v>
+        <v>113.01</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1762</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>0.2772</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="P57" t="n">
-        <v>0.1542</v>
+        <v>0.9789</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S57" t="b">
@@ -4689,18 +4629,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C58" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -4730,23 +4670,23 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.85</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>0.198</v>
+        <v>0.8753</v>
       </c>
       <c r="O58" t="n">
-        <v>0.3129</v>
+        <v>0.9675</v>
       </c>
       <c r="P58" t="n">
-        <v>0.1693</v>
+        <v>0.8824</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S58" t="b">
@@ -4761,29 +4701,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C59" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E59" t="b">
         <v>1</v>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>200</v>
@@ -4796,29 +4740,25 @@
       <c r="K59" t="n">
         <v>200</v>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>4.19</v>
+        <v>23.47</v>
       </c>
       <c r="N59" t="n">
-        <v>0.2079</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.3149</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.1821</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S59" t="b">
@@ -4833,22 +4773,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C60" t="n">
-        <v>274</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -4859,42 +4795,38 @@
         </is>
       </c>
       <c r="H60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K60" t="n">
         <v>200</v>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>18.22</v>
+        <v>0.06</v>
       </c>
       <c r="N60" t="n">
-        <v>0.396</v>
+        <v>0.8293</v>
       </c>
       <c r="O60" t="n">
-        <v>0.4653</v>
+        <v>0.9079</v>
       </c>
       <c r="P60" t="n">
-        <v>0.362</v>
+        <v>0.8659</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S60" t="b">
@@ -4909,40 +4841,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C61" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E61" t="b">
         <v>1</v>
       </c>
       <c r="F61" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4954,23 +4882,23 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>12.14</v>
+        <v>1.73</v>
       </c>
       <c r="N61" t="n">
-        <v>0.3446</v>
+        <v>0.7696</v>
       </c>
       <c r="O61" t="n">
-        <v>0.4059</v>
+        <v>0.9051</v>
       </c>
       <c r="P61" t="n">
-        <v>0.3101</v>
+        <v>0.8026</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S61" t="b">
@@ -4985,14 +4913,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C62" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5011,14 +4939,14 @@
         </is>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -5030,23 +4958,23 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>78.7</v>
+        <v>3.01</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4931</v>
+        <v>0.8753</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5604</v>
+        <v>0.9675</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4461</v>
+        <v>0.8834</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S62" t="b">
@@ -5061,18 +4989,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C63" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -5083,7 +5011,7 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>200</v>
@@ -5102,23 +5030,23 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>61.05</v>
+        <v>0.77</v>
       </c>
       <c r="N63" t="n">
-        <v>0.4653</v>
+        <v>0.9079</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6713</v>
+        <v>0.9675</v>
       </c>
       <c r="P63" t="n">
-        <v>0.4265</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S63" t="b">
@@ -5133,14 +5061,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C64" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5151,15 +5079,11 @@
         <v>1</v>
       </c>
       <c r="F64" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>200</v>
@@ -5178,23 +5102,23 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>4.3</v>
+        <v>37.46</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2158</v>
+        <v>0.981</v>
       </c>
       <c r="O64" t="n">
-        <v>0.3248</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0.1926</v>
+        <v>0.9821</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S64" t="b">
@@ -5209,14 +5133,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C65" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5248,29 +5172,25 @@
       <c r="K65" t="n">
         <v>200</v>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>91.92</v>
+        <v>46.7</v>
       </c>
       <c r="N65" t="n">
-        <v>0.5208</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>0.6198</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.4716</v>
+        <v>0.9876</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S65" t="b">
@@ -5285,18 +5205,18 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C66" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -5314,39 +5234,35 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K66" t="n">
         <v>200</v>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>12.04</v>
+        <v>26.37</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2752</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.3267</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.2558</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S66" t="b">
@@ -5361,14 +5277,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>cowdataset</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1573</v>
+        <v>1019</v>
       </c>
       <c r="C67" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5406,23 +5322,23 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>12.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3426</v>
+        <v>0.981</v>
       </c>
       <c r="O67" t="n">
-        <v>0.4099</v>
+        <v>0.9973</v>
       </c>
       <c r="P67" t="n">
-        <v>0.31</v>
+        <v>0.9838</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>time-aware</t>
         </is>
       </c>
       <c r="S67" t="b">
@@ -5437,36 +5353,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>elpephants</t>
+          <t>ctai</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1573</v>
+        <v>4145</v>
       </c>
       <c r="C68" t="n">
-        <v>274</v>
+        <v>72</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E68" t="b">
         <v>1</v>
       </c>
       <c r="F68" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -5478,27 +5398,27 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1.2</v>
+        <v>7.51</v>
       </c>
       <c r="N68" t="n">
-        <v>0.2139</v>
+        <v>0.8875</v>
       </c>
       <c r="O68" t="n">
-        <v>0.3564</v>
+        <v>0.9282</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1962</v>
+        <v>0.8982</v>
       </c>
       <c r="Q68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>original_split</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5509,14 +5429,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>giraffes</t>
+          <t>ctai</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1125</v>
+        <v>4145</v>
       </c>
       <c r="C69" t="n">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5535,7 +5455,7 @@
         </is>
       </c>
       <c r="H69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>50</v>
@@ -5554,16 +5474,16 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>3.66</v>
+        <v>24.55</v>
       </c>
       <c r="N69" t="n">
-        <v>0.9366</v>
+        <v>0.8821</v>
       </c>
       <c r="O69" t="n">
-        <v>0.959</v>
+        <v>0.9271</v>
       </c>
       <c r="P69" t="n">
-        <v>0.9287</v>
+        <v>0.8888</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
@@ -5585,40 +5505,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mpdd</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1325</v>
+        <v>1686</v>
       </c>
       <c r="C70" t="n">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E70" t="b">
         <v>1</v>
       </c>
       <c r="F70" t="b">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -5630,27 +5546,27 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4.31</v>
+        <v>1.31</v>
       </c>
       <c r="N70" t="n">
-        <v>0.9106</v>
+        <v>0.6832</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9593</v>
+        <v>0.8723</v>
       </c>
       <c r="P70" t="n">
-        <v>0.8934</v>
+        <v>0.6791</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5661,14 +5577,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mpdd</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1325</v>
+        <v>1686</v>
       </c>
       <c r="C71" t="n">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5679,22 +5595,18 @@
         <v>1</v>
       </c>
       <c r="F71" t="b">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="b">
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5706,27 +5618,27 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>6.5</v>
+        <v>29.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0.9106</v>
+        <v>0.8818</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9553</v>
+        <v>0.9598</v>
       </c>
       <c r="P71" t="n">
-        <v>0.8954</v>
+        <v>0.88</v>
       </c>
       <c r="Q71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5737,22 +5649,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>polarbearvidid</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1114</v>
+        <v>1686</v>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -5763,14 +5671,14 @@
         </is>
       </c>
       <c r="H72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -5782,27 +5690,27 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3.48</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>0.8276</v>
+        <v>0.9882</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9882</v>
       </c>
       <c r="P72" t="n">
-        <v>0.8279</v>
+        <v>0.9882</v>
       </c>
       <c r="Q72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5813,14 +5721,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>polarbearvidid</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1114</v>
+        <v>1686</v>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5831,22 +5739,18 @@
         <v>1</v>
       </c>
       <c r="F73" t="b">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5858,27 +5762,27 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="N73" t="n">
-        <v>0.8506</v>
+        <v>0.7612</v>
       </c>
       <c r="O73" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9054</v>
       </c>
       <c r="P73" t="n">
-        <v>0.8499</v>
+        <v>0.7568</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5889,40 +5793,36 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>reunionturtles</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>237</v>
+        <v>1686</v>
       </c>
       <c r="C74" t="n">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E74" t="b">
         <v>1</v>
       </c>
       <c r="F74" t="b">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5934,27 +5834,27 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>3.28</v>
+        <v>1.23</v>
       </c>
       <c r="N74" t="n">
-        <v>0.5823</v>
+        <v>0.6478</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8354</v>
+        <v>0.8227</v>
       </c>
       <c r="P74" t="n">
-        <v>0.5232</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="Q74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5965,14 +5865,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>reunionturtles</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>237</v>
+        <v>1686</v>
       </c>
       <c r="C75" t="n">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5983,22 +5883,18 @@
         <v>1</v>
       </c>
       <c r="F75" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -6010,27 +5906,27 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>2.32</v>
+        <v>35.31</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4557</v>
+        <v>0.7612</v>
       </c>
       <c r="O75" t="n">
-        <v>0.8101</v>
+        <v>0.9054</v>
       </c>
       <c r="P75" t="n">
-        <v>0.3835</v>
+        <v>0.7568</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>similarity-aware</t>
+          <t>random</t>
         </is>
       </c>
       <c r="S75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6041,18 +5937,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1663</v>
+        <v>1686</v>
       </c>
       <c r="C76" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -6082,16 +5978,16 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1.21</v>
+        <v>0.41</v>
       </c>
       <c r="N76" t="n">
-        <v>0.5707</v>
+        <v>0.6974</v>
       </c>
       <c r="O76" t="n">
-        <v>0.7722</v>
+        <v>0.8345</v>
       </c>
       <c r="P76" t="n">
-        <v>0.5642</v>
+        <v>0.6947</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
@@ -6113,14 +6009,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1663</v>
+        <v>1686</v>
       </c>
       <c r="C77" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6142,11 +6038,11 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -6158,16 +6054,16 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>11.49</v>
+        <v>29.34</v>
       </c>
       <c r="N77" t="n">
-        <v>0.8393</v>
+        <v>0.9858</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8729</v>
+        <v>0.9929</v>
       </c>
       <c r="P77" t="n">
-        <v>0.8296</v>
+        <v>0.9858</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
@@ -6189,27 +6085,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>czoo</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1663</v>
+        <v>1686</v>
       </c>
       <c r="C78" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E78" t="b">
         <v>1</v>
       </c>
       <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
@@ -6230,16 +6130,16 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0.65</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>0.5875</v>
+        <v>0.9905</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7362</v>
+        <v>0.9905</v>
       </c>
       <c r="P78" t="n">
-        <v>0.586</v>
+        <v>0.9905</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
@@ -6261,29 +6161,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C79" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E79" t="b">
         <v>1</v>
       </c>
       <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
         <v>200</v>
@@ -6302,27 +6206,27 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0.8</v>
+        <v>91.92</v>
       </c>
       <c r="N79" t="n">
-        <v>0.5971</v>
+        <v>0.5208</v>
       </c>
       <c r="O79" t="n">
-        <v>0.7938</v>
+        <v>0.6198</v>
       </c>
       <c r="P79" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.4716</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6333,33 +6237,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C80" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E80" t="b">
         <v>1</v>
       </c>
       <c r="F80" t="b">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>200</v>
@@ -6378,27 +6278,27 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>81.47</v>
+        <v>1.2</v>
       </c>
       <c r="N80" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.2139</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8897</v>
+        <v>0.3564</v>
       </c>
       <c r="P80" t="n">
-        <v>0.844</v>
+        <v>0.1962</v>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6409,31 +6309,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C81" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>superpoint</t>
         </is>
       </c>
       <c r="E81" t="b">
         <v>1</v>
       </c>
       <c r="F81" t="b">
-        <v>1</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="b">
         <v>0</v>
       </c>
@@ -6454,27 +6350,27 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="N81" t="n">
-        <v>0.7938</v>
+        <v>0.198</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8273</v>
+        <v>0.3129</v>
       </c>
       <c r="P81" t="n">
-        <v>0.786</v>
+        <v>0.1693</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6485,18 +6381,18 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C82" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>aliked</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -6511,46 +6407,42 @@
         </is>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>isotonic</t>
+          <t>isotonic_pchip</t>
         </is>
       </c>
       <c r="K82" t="n">
         <v>200</v>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>4.7</v>
+        <v>5.66</v>
       </c>
       <c r="N82" t="n">
-        <v>0.7986</v>
+        <v>0.396</v>
       </c>
       <c r="O82" t="n">
-        <v>0.8321</v>
+        <v>0.4634</v>
       </c>
       <c r="P82" t="n">
-        <v>0.7915</v>
+        <v>0.3641</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -6561,18 +6453,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C83" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -6602,27 +6494,27 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="N83" t="n">
-        <v>0.6451</v>
+        <v>0.1762</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8249</v>
+        <v>0.2772</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6417</v>
+        <v>0.1542</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -6633,14 +6525,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C84" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6651,9 +6543,13 @@
         <v>1</v>
       </c>
       <c r="F84" t="b">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H84" t="b">
         <v>1</v>
       </c>
@@ -6668,33 +6564,29 @@
       <c r="K84" t="n">
         <v>200</v>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>19.46</v>
+        <v>67.95</v>
       </c>
       <c r="N84" t="n">
-        <v>0.789</v>
+        <v>0.5208</v>
       </c>
       <c r="O84" t="n">
-        <v>0.8729</v>
+        <v>0.6198</v>
       </c>
       <c r="P84" t="n">
-        <v>0.7766</v>
+        <v>0.4716</v>
       </c>
       <c r="Q84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6705,14 +6597,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sealid</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1663</v>
+        <v>1573</v>
       </c>
       <c r="C85" t="n">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6750,27 +6642,27 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>11.57</v>
+        <v>78.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0.8129</v>
+        <v>0.4931</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8537</v>
+        <v>0.5604</v>
       </c>
       <c r="P85" t="n">
-        <v>0.8084</v>
+        <v>0.4461</v>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6781,14 +6673,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C86" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6810,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6826,23 +6718,23 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>98.36</v>
+        <v>12.14</v>
       </c>
       <c r="N86" t="n">
-        <v>0.7628</v>
+        <v>0.3446</v>
       </c>
       <c r="O86" t="n">
-        <v>0.8791</v>
+        <v>0.4059</v>
       </c>
       <c r="P86" t="n">
-        <v>0.7481</v>
+        <v>0.3101</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S86" t="b">
@@ -6857,29 +6749,29 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C87" t="n">
-        <v>91</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>200</v>
@@ -6892,29 +6784,25 @@
       <c r="K87" t="n">
         <v>200</v>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>17.19</v>
+        <v>0.09</v>
       </c>
       <c r="N87" t="n">
-        <v>0.7721</v>
+        <v>0.1366</v>
       </c>
       <c r="O87" t="n">
-        <v>0.8558</v>
+        <v>0.2178</v>
       </c>
       <c r="P87" t="n">
-        <v>0.764</v>
+        <v>0.1158</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S87" t="b">
@@ -6929,27 +6817,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C88" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>aliked</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E88" t="b">
         <v>1</v>
       </c>
       <c r="F88" t="b">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H88" t="b">
         <v>0</v>
       </c>
@@ -6970,23 +6862,23 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0.507</v>
+        <v>0.2158</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8047</v>
+        <v>0.3248</v>
       </c>
       <c r="P88" t="n">
-        <v>0.4683</v>
+        <v>0.1926</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S88" t="b">
@@ -7001,14 +6893,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C89" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7042,23 +6934,23 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>2.62</v>
+        <v>4.19</v>
       </c>
       <c r="N89" t="n">
-        <v>0.6884</v>
+        <v>0.2079</v>
       </c>
       <c r="O89" t="n">
-        <v>0.8558</v>
+        <v>0.3149</v>
       </c>
       <c r="P89" t="n">
-        <v>0.6792</v>
+        <v>0.1821</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S89" t="b">
@@ -7073,14 +6965,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C90" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7091,15 +6983,11 @@
         <v>1</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -7118,23 +7006,23 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>2.52</v>
+        <v>61.05</v>
       </c>
       <c r="N90" t="n">
-        <v>0.6279</v>
+        <v>0.4653</v>
       </c>
       <c r="O90" t="n">
-        <v>0.8279</v>
+        <v>0.6713</v>
       </c>
       <c r="P90" t="n">
-        <v>0.607</v>
+        <v>0.4265</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S90" t="b">
@@ -7149,32 +7037,36 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C91" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E91" t="b">
         <v>1</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -7184,29 +7076,25 @@
       <c r="K91" t="n">
         <v>200</v>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>late</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>1.22</v>
+        <v>13.12</v>
       </c>
       <c r="N91" t="n">
-        <v>0.6512</v>
+        <v>0.4079</v>
       </c>
       <c r="O91" t="n">
-        <v>0.8186</v>
+        <v>0.4614</v>
       </c>
       <c r="P91" t="n">
-        <v>0.6382</v>
+        <v>0.3584</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S91" t="b">
@@ -7221,36 +7109,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C92" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>superpoint</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E92" t="b">
         <v>1</v>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="H92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -7262,23 +7154,23 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0.78</v>
+        <v>12.29</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6047</v>
+        <v>0.3426</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8279</v>
+        <v>0.4099</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5925</v>
+        <v>0.31</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S92" t="b">
@@ -7293,14 +7185,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>seastarreid2023</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1862</v>
+        <v>1573</v>
       </c>
       <c r="C93" t="n">
-        <v>91</v>
+        <v>274</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7322,11 +7214,11 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>isotonic_pchip</t>
+          <t>isotonic</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -7338,23 +7230,23 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>82.66</v>
+        <v>12.04</v>
       </c>
       <c r="N93" t="n">
-        <v>0.7721</v>
+        <v>0.2752</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8558</v>
+        <v>0.3267</v>
       </c>
       <c r="P93" t="n">
-        <v>0.7685</v>
+        <v>0.2558</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>time-aware</t>
+          <t>original_split</t>
         </is>
       </c>
       <c r="S93" t="b">
@@ -7369,14 +7261,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>stripespotter</t>
+          <t>elpephants</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>660</v>
+        <v>1573</v>
       </c>
       <c r="C94" t="n">
-        <v>46</v>
+        <v>274</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7414,29 +7306,2245 @@
         </is>
       </c>
       <c r="M94" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>original_split</t>
+        </is>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>giraffes</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C95" t="n">
+        <v>178</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>50</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>200</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.9366</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="Q95" t="b">
+        <v>1</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>mpdd</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C96" t="n">
+        <v>182</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>20</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>200</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="Q96" t="b">
+        <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S96" t="b">
+        <v>0</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>mpdd</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1325</v>
+      </c>
+      <c r="C97" t="n">
+        <v>182</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>50</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>200</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.8954</v>
+      </c>
+      <c r="Q97" t="b">
+        <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S97" t="b">
+        <v>0</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>polarbearvidid</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1114</v>
+      </c>
+      <c r="C98" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>20</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>200</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.8506</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.8499</v>
+      </c>
+      <c r="Q98" t="b">
+        <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S98" t="b">
+        <v>0</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>polarbearvidid</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1114</v>
+      </c>
+      <c r="C99" t="n">
+        <v>12</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>50</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>200</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.8276</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S99" t="b">
+        <v>0</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>reunionturtles</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>237</v>
+      </c>
+      <c r="C100" t="n">
+        <v>79</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>50</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>200</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S100" t="b">
+        <v>0</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>reunionturtles</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>237</v>
+      </c>
+      <c r="C101" t="n">
+        <v>79</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>20</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>200</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.8101</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="Q101" t="b">
+        <v>0</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>similarity-aware</t>
+        </is>
+      </c>
+      <c r="S101" t="b">
+        <v>0</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C102" t="n">
+        <v>57</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>aliked</t>
+        </is>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>200</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>200</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.7362</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q102" t="b">
+        <v>1</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S102" t="b">
+        <v>1</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C103" t="n">
+        <v>57</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>200</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>200</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="Q103" t="b">
+        <v>1</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S103" t="b">
+        <v>1</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C104" t="n">
+        <v>57</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H104" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>50</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>200</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.8296</v>
+      </c>
+      <c r="Q104" t="b">
+        <v>1</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S104" t="b">
+        <v>1</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C105" t="n">
+        <v>57</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H105" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>200</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>200</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>81.47</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="Q105" t="b">
+        <v>1</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S105" t="b">
+        <v>1</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C106" t="n">
+        <v>57</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>superpoint</t>
+        </is>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="b">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>200</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>200</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.5971</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="Q106" t="b">
+        <v>1</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S106" t="b">
+        <v>1</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C107" t="n">
+        <v>57</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" t="b">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>200</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>200</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.7722</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="Q107" t="b">
+        <v>1</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S107" t="b">
+        <v>1</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C108" t="n">
+        <v>57</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>200</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>200</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.7938</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="Q108" t="b">
+        <v>1</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S108" t="b">
+        <v>1</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C109" t="n">
+        <v>57</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="b">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="b">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>200</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>200</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.7766</v>
+      </c>
+      <c r="Q109" t="b">
+        <v>1</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S109" t="b">
+        <v>1</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C110" t="n">
+        <v>57</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H110" t="b">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>50</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>200</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.8129</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="Q110" t="b">
+        <v>1</v>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S110" t="b">
+        <v>1</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C111" t="n">
+        <v>57</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" t="b">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>200</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>200</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="Q111" t="b">
+        <v>1</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S111" t="b">
+        <v>1</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C112" t="n">
+        <v>57</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>200</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>200</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.7962</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.7786</v>
+      </c>
+      <c r="Q112" t="b">
+        <v>1</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S112" t="b">
+        <v>1</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sealid</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1663</v>
+      </c>
+      <c r="C113" t="n">
+        <v>57</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H113" t="b">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>50</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>200</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.7986</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.8321</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="Q113" t="b">
+        <v>1</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="S113" t="b">
+        <v>1</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C114" t="n">
+        <v>91</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H114" t="b">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>200</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>200</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="Q114" t="b">
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S114" t="b">
+        <v>0</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C115" t="n">
+        <v>91</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" t="b">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>200</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>200</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="Q115" t="b">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S115" t="b">
+        <v>0</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C116" t="n">
+        <v>91</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" t="b">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>200</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>200</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.8186</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="Q116" t="b">
+        <v>0</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S116" t="b">
+        <v>0</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C117" t="n">
+        <v>91</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>superpoint</t>
+        </is>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+      <c r="F117" t="b">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>200</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>200</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.8279</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="Q117" t="b">
+        <v>0</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S117" t="b">
+        <v>0</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C118" t="n">
+        <v>91</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>aliked</t>
+        </is>
+      </c>
+      <c r="E118" t="b">
+        <v>1</v>
+      </c>
+      <c r="F118" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>200</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>200</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.8047</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="Q118" t="b">
+        <v>0</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S118" t="b">
+        <v>0</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C119" t="n">
+        <v>91</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H119" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>200</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>200</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>82.66</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.7685</v>
+      </c>
+      <c r="Q119" t="b">
+        <v>0</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S119" t="b">
+        <v>0</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C120" t="n">
+        <v>91</v>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>200</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>200</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.7349</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="Q120" t="b">
+        <v>0</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S120" t="b">
+        <v>0</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C121" t="n">
+        <v>91</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E121" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" t="b">
+        <v>0</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>200</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>200</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="Q121" t="b">
+        <v>0</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S121" t="b">
+        <v>0</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C122" t="n">
+        <v>91</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E122" t="b">
+        <v>1</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H122" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>200</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>isotonic_pchip</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>200</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.7685</v>
+      </c>
+      <c r="Q122" t="b">
+        <v>0</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S122" t="b">
+        <v>0</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>seastarreid2023</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C123" t="n">
+        <v>91</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H123" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n">
+        <v>50</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>200</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.7628</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.7481</v>
+      </c>
+      <c r="Q123" t="b">
+        <v>0</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>time-aware</t>
+        </is>
+      </c>
+      <c r="S123" t="b">
+        <v>0</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>stripespotter</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>660</v>
+      </c>
+      <c r="C124" t="n">
+        <v>46</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="H124" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>50</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>isotonic</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>200</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>late</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
         <v>4.52</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N124" t="n">
         <v>0.9756</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O124" t="n">
         <v>0.9817</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P124" t="n">
         <v>0.9752999999999999</v>
       </c>
-      <c r="Q94" t="b">
-        <v>1</v>
-      </c>
-      <c r="R94" t="inlineStr">
+      <c r="Q124" t="b">
+        <v>1</v>
+      </c>
+      <c r="R124" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="S94" t="b">
-        <v>1</v>
-      </c>
-      <c r="T94" t="inlineStr">
+      <c r="S124" t="b">
+        <v>1</v>
+      </c>
+      <c r="T124" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
